--- a/RESULTS/tables/survival_time_dependent_auc.xlsx
+++ b/RESULTS/tables/survival_time_dependent_auc.xlsx
@@ -482,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9189177900056967</v>
+        <v>0.9218511615675944</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9105182789008714</v>
+        <v>0.9226726403241846</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9008690493152487</v>
+        <v>0.916741643019816</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8909387901977208</v>
+        <v>0.9064271708610475</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8846240084762689</v>
+        <v>0.8983194936168155</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.906986659826706</v>
+        <v>0.9159954830259727</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9120939094210936</v>
+        <v>0.9235442428191195</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9012571231158502</v>
+        <v>0.9176651166541878</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8931249557921167</v>
+        <v>0.9081877558531236</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8891275693701755</v>
+        <v>0.9021079076466514</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
